--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:37:23+00:00</t>
+    <t>2024-10-25T08:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:22:33+00:00</t>
+    <t>2024-10-28T11:11:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:11:19+00:00</t>
+    <t>2024-10-28T11:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:26:59+00:00</t>
+    <t>2024-10-29T09:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:20:35+00:00</t>
+    <t>2024-10-31T11:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T11:17:53+00:00</t>
+    <t>2024-10-31T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:29:56+00:00</t>
+    <t>2024-11-05T14:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:48:02+00:00</t>
+    <t>2024-11-07T21:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -36,73 +36,79 @@
     <t>Name</t>
   </si>
   <si>
+    <t>SonderklasseVS</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Sonderklasse ValueSet</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-11-12T20:06:39+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Example Publisher</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Example Publisher (http://example.org/example-publisher)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet für die Klasse (KaOrg)</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Immutable</t>
+  </si>
+  <si>
+    <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Allgemeine Gebührenklasse</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
     <t>Sonderklasse</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>draft</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-11-12T08:47:06+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>Example Publisher</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ValueSet für die Klasse (KaOrg)</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Immutable</t>
-  </si>
-  <si>
-    <t>BooleanType[null]</t>
-  </si>
-  <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Allgemeine Gebührenklasse</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
   <si>
     <t>System URI</t>
@@ -286,81 +292,81 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -379,42 +385,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T18:55:56+00:00</t>
+    <t>2024-11-15T19:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:04:50+00:00</t>
+    <t>2024-11-15T19:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:21:45+00:00</t>
+    <t>2024-11-15T20:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:14:47+00:00</t>
+    <t>2024-11-17T19:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:44:33+00:00</t>
+    <t>2024-11-19T10:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/ValueSet-moped-Sonderklasse-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T10:30:26+00:00</t>
+    <t>2025-02-10T09:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
